--- a/annotations JL.xlsx
+++ b/annotations JL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jean-\Desktop\Cours ENSAE\3A ENSAE\NLP\Projet final\NLP_ENSAE_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C165744B-C593-402B-8F3F-AE7AAFCAC067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1807FCE5-3E91-42D3-AEE5-C58A23E32E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{89D58ADA-68C1-4510-AD5E-1C4D340B6593}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Texte</t>
   </si>
   <si>
-    <t>LDB (=1 si LDB, 0 sinon)</t>
-  </si>
-  <si>
     <t>ENTENTE DES ÉCOLOGISTES LES VERTS GÉNÉRATION ÉCOLOGIE</t>
   </si>
   <si>
@@ -943,9 +940,6 @@
 ABSTENTIONNISTES, DIMANCHE LE RÉSULTAT DÉPEND DE VOUS</t>
   </si>
   <si>
-    <t>Courant Politique (GR,G,C,D,DR,I)</t>
-  </si>
-  <si>
     <t>Madame, Mademoiselle, Monsieur,
 Depuis 1988, je suis la candidate présentée par le Parti Communiste Français dans cette 6e circonscription.
 Vous savez mon attachement à l'honnêteté et à la morale en politique, mon rejet des jeux politiciens.</t>
@@ -1522,6 +1516,12 @@
   </si>
   <si>
     <t>Je compte sur vous pour m'apporter votre soutien dans la réalisation de cet immense chantier, difficile mais exhaltant, car je crois que c'est la voie de l'avenir pour sortir de la crise actuelle.</t>
+  </si>
+  <si>
+    <t>LDB</t>
+  </si>
+  <si>
+    <t>Courant Politique</t>
   </si>
 </sst>
 </file>
@@ -1915,24 +1915,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1954,13 +1954,13 @@
     </row>
     <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1968,13 +1968,13 @@
     </row>
     <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1982,13 +1982,13 @@
     </row>
     <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="7" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2010,13 +2010,13 @@
     </row>
     <row r="8" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2024,13 +2024,13 @@
     </row>
     <row r="9" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2038,13 +2038,13 @@
     </row>
     <row r="10" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2052,13 +2052,13 @@
     </row>
     <row r="11" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2066,13 +2066,13 @@
     </row>
     <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2094,13 +2094,13 @@
     </row>
     <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2108,13 +2108,13 @@
     </row>
     <row r="15" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2122,13 +2122,13 @@
     </row>
     <row r="16" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2136,13 +2136,13 @@
     </row>
     <row r="17" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2164,13 +2164,13 @@
     </row>
     <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="20" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2192,13 +2192,13 @@
     </row>
     <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2206,13 +2206,13 @@
     </row>
     <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2220,13 +2220,13 @@
     </row>
     <row r="23" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2248,13 +2248,13 @@
     </row>
     <row r="25" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2262,13 +2262,13 @@
     </row>
     <row r="26" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2276,13 +2276,13 @@
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2290,13 +2290,13 @@
     </row>
     <row r="28" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2304,13 +2304,13 @@
     </row>
     <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2318,13 +2318,13 @@
     </row>
     <row r="30" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2332,13 +2332,13 @@
     </row>
     <row r="31" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2346,13 +2346,13 @@
     </row>
     <row r="32" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2360,13 +2360,13 @@
     </row>
     <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2374,13 +2374,13 @@
     </row>
     <row r="34" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2388,13 +2388,13 @@
     </row>
     <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2402,13 +2402,13 @@
     </row>
     <row r="36" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2430,13 +2430,13 @@
     </row>
     <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2444,13 +2444,13 @@
     </row>
     <row r="39" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2458,13 +2458,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="41" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2486,13 +2486,13 @@
     </row>
     <row r="42" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
-        <v>55</v>
-      </c>
       <c r="C42" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2500,13 +2500,13 @@
     </row>
     <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
         <v>54</v>
       </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
       <c r="C43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2514,13 +2514,13 @@
     </row>
     <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
         <v>54</v>
       </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
       <c r="C44" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2528,13 +2528,13 @@
     </row>
     <row r="45" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
         <v>54</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2542,13 +2542,13 @@
     </row>
     <row r="46" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
         <v>54</v>
       </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2556,13 +2556,13 @@
     </row>
     <row r="47" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" t="s">
         <v>54</v>
       </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
       <c r="C47" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2570,13 +2570,13 @@
     </row>
     <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" t="s">
         <v>54</v>
       </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2584,13 +2584,13 @@
     </row>
     <row r="49" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
         <v>54</v>
       </c>
-      <c r="B49" t="s">
-        <v>55</v>
-      </c>
       <c r="C49" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2598,13 +2598,13 @@
     </row>
     <row r="50" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
         <v>54</v>
       </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
       <c r="C50" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2612,13 +2612,13 @@
     </row>
     <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
         <v>54</v>
       </c>
-      <c r="B51" t="s">
-        <v>55</v>
-      </c>
       <c r="C51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2626,13 +2626,13 @@
     </row>
     <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
         <v>54</v>
       </c>
-      <c r="B52" t="s">
-        <v>55</v>
-      </c>
       <c r="C52" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2640,13 +2640,13 @@
     </row>
     <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
         <v>54</v>
       </c>
-      <c r="B53" t="s">
-        <v>55</v>
-      </c>
       <c r="C53" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="54" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="B54" t="s">
-        <v>55</v>
-      </c>
       <c r="C54" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2668,13 +2668,13 @@
     </row>
     <row r="55" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>55</v>
-      </c>
       <c r="C55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2682,13 +2682,13 @@
     </row>
     <row r="56" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
-        <v>55</v>
-      </c>
       <c r="C56" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2696,13 +2696,13 @@
     </row>
     <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>55</v>
-      </c>
       <c r="C57" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="58" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" t="s">
-        <v>55</v>
-      </c>
       <c r="C58" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2724,13 +2724,13 @@
     </row>
     <row r="59" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" t="s">
         <v>54</v>
       </c>
-      <c r="B59" t="s">
-        <v>55</v>
-      </c>
       <c r="C59" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2738,13 +2738,13 @@
     </row>
     <row r="60" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" t="s">
         <v>54</v>
       </c>
-      <c r="B60" t="s">
-        <v>55</v>
-      </c>
       <c r="C60" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="61" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2766,13 +2766,13 @@
     </row>
     <row r="62" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B62" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2780,13 +2780,13 @@
     </row>
     <row r="63" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="64" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2808,13 +2808,13 @@
     </row>
     <row r="65" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2822,13 +2822,13 @@
     </row>
     <row r="66" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2836,13 +2836,13 @@
     </row>
     <row r="67" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2850,13 +2850,13 @@
     </row>
     <row r="68" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2864,13 +2864,13 @@
     </row>
     <row r="69" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2878,13 +2878,13 @@
     </row>
     <row r="70" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="71" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2906,13 +2906,13 @@
     </row>
     <row r="72" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2920,13 +2920,13 @@
     </row>
     <row r="73" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2934,13 +2934,13 @@
     </row>
     <row r="74" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2962,13 +2962,13 @@
     </row>
     <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2976,13 +2976,13 @@
     </row>
     <row r="77" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2990,13 +2990,13 @@
     </row>
     <row r="78" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3004,13 +3004,13 @@
     </row>
     <row r="79" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3018,13 +3018,13 @@
     </row>
     <row r="80" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3032,13 +3032,13 @@
     </row>
     <row r="81" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3046,13 +3046,13 @@
     </row>
     <row r="82" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3060,13 +3060,13 @@
     </row>
     <row r="83" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3074,13 +3074,13 @@
     </row>
     <row r="84" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3088,13 +3088,13 @@
     </row>
     <row r="85" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3102,13 +3102,13 @@
     </row>
     <row r="86" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B86" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="87" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="88" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3144,13 +3144,13 @@
     </row>
     <row r="89" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3158,13 +3158,13 @@
     </row>
     <row r="90" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3172,13 +3172,13 @@
     </row>
     <row r="91" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3186,13 +3186,13 @@
     </row>
     <row r="92" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3200,13 +3200,13 @@
     </row>
     <row r="93" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3214,13 +3214,13 @@
     </row>
     <row r="94" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3228,13 +3228,13 @@
     </row>
     <row r="95" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3242,13 +3242,13 @@
     </row>
     <row r="96" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="97" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3270,13 +3270,13 @@
     </row>
     <row r="98" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3284,13 +3284,13 @@
     </row>
     <row r="99" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="100" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3312,13 +3312,13 @@
     </row>
     <row r="101" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3326,13 +3326,13 @@
     </row>
     <row r="102" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3340,13 +3340,13 @@
     </row>
     <row r="103" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3354,13 +3354,13 @@
     </row>
     <row r="104" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="105" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3382,13 +3382,13 @@
     </row>
     <row r="106" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3396,13 +3396,13 @@
     </row>
     <row r="107" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3410,13 +3410,13 @@
     </row>
     <row r="108" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="109" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3438,13 +3438,13 @@
     </row>
     <row r="110" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3452,13 +3452,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3466,13 +3466,13 @@
     </row>
     <row r="112" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3480,13 +3480,13 @@
     </row>
     <row r="113" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3494,13 +3494,13 @@
     </row>
     <row r="114" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="115" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3522,13 +3522,13 @@
     </row>
     <row r="116" spans="1:4" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3536,13 +3536,13 @@
     </row>
     <row r="117" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3550,13 +3550,13 @@
     </row>
     <row r="118" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -3564,13 +3564,13 @@
     </row>
     <row r="119" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3578,13 +3578,13 @@
     </row>
     <row r="120" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3592,13 +3592,13 @@
     </row>
     <row r="121" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3606,13 +3606,13 @@
     </row>
     <row r="122" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -3620,13 +3620,13 @@
     </row>
     <row r="123" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -3634,13 +3634,13 @@
     </row>
     <row r="124" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3648,13 +3648,13 @@
     </row>
     <row r="125" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3662,13 +3662,13 @@
     </row>
     <row r="126" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -3676,13 +3676,13 @@
     </row>
     <row r="127" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -3690,13 +3690,13 @@
     </row>
     <row r="128" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3704,13 +3704,13 @@
     </row>
     <row r="129" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -3718,13 +3718,13 @@
     </row>
     <row r="130" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -3732,13 +3732,13 @@
     </row>
     <row r="131" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -3746,13 +3746,13 @@
     </row>
     <row r="132" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="133" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -3774,13 +3774,13 @@
     </row>
     <row r="134" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -3788,13 +3788,13 @@
     </row>
     <row r="135" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -3802,13 +3802,13 @@
     </row>
     <row r="136" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -3816,13 +3816,13 @@
     </row>
     <row r="137" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -3830,13 +3830,13 @@
     </row>
     <row r="138" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -3844,13 +3844,13 @@
     </row>
     <row r="139" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -3858,13 +3858,13 @@
     </row>
     <row r="140" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -3872,13 +3872,13 @@
     </row>
     <row r="141" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3886,13 +3886,13 @@
     </row>
     <row r="142" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -3900,13 +3900,13 @@
     </row>
     <row r="143" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -3914,13 +3914,13 @@
     </row>
     <row r="144" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -3928,13 +3928,13 @@
     </row>
     <row r="145" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -3942,13 +3942,13 @@
     </row>
     <row r="146" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -3956,13 +3956,13 @@
     </row>
     <row r="147" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -3970,13 +3970,13 @@
     </row>
     <row r="148" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -3984,13 +3984,13 @@
     </row>
     <row r="149" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -3998,13 +3998,13 @@
     </row>
     <row r="150" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4012,13 +4012,13 @@
     </row>
     <row r="151" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4026,13 +4026,13 @@
     </row>
     <row r="152" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4040,13 +4040,13 @@
     </row>
     <row r="153" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -4054,13 +4054,13 @@
     </row>
     <row r="154" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4068,13 +4068,13 @@
     </row>
     <row r="155" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="156" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4096,13 +4096,13 @@
     </row>
     <row r="157" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B157" t="s">
-        <v>12</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -4110,13 +4110,13 @@
     </row>
     <row r="158" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="159" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -4138,13 +4138,13 @@
     </row>
     <row r="160" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -4152,13 +4152,13 @@
     </row>
     <row r="161" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -4166,13 +4166,13 @@
     </row>
     <row r="162" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -4180,13 +4180,13 @@
     </row>
     <row r="163" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -4194,13 +4194,13 @@
     </row>
     <row r="164" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -4208,13 +4208,13 @@
     </row>
     <row r="165" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -4222,13 +4222,13 @@
     </row>
     <row r="166" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="167" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -4250,13 +4250,13 @@
     </row>
     <row r="168" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -4264,13 +4264,13 @@
     </row>
     <row r="169" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -4278,13 +4278,13 @@
     </row>
     <row r="170" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -4292,13 +4292,13 @@
     </row>
     <row r="171" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4306,13 +4306,13 @@
     </row>
     <row r="172" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -4320,13 +4320,13 @@
     </row>
     <row r="173" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -4334,13 +4334,13 @@
     </row>
     <row r="174" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4348,13 +4348,13 @@
     </row>
     <row r="175" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -4362,13 +4362,13 @@
     </row>
     <row r="176" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -4376,13 +4376,13 @@
     </row>
     <row r="177" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -4390,13 +4390,13 @@
     </row>
     <row r="178" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="179" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -4418,13 +4418,13 @@
     </row>
     <row r="180" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B180" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -4432,13 +4432,13 @@
     </row>
     <row r="181" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B181" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4446,13 +4446,13 @@
     </row>
     <row r="182" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -4460,13 +4460,13 @@
     </row>
     <row r="183" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B183" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -4474,13 +4474,13 @@
     </row>
     <row r="184" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -4488,13 +4488,13 @@
     </row>
     <row r="185" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4502,13 +4502,13 @@
     </row>
     <row r="186" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>53</v>
+      </c>
+      <c r="B186" t="s">
         <v>54</v>
       </c>
-      <c r="B186" t="s">
-        <v>55</v>
-      </c>
       <c r="C186" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -4516,13 +4516,13 @@
     </row>
     <row r="187" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>53</v>
+      </c>
+      <c r="B187" t="s">
         <v>54</v>
       </c>
-      <c r="B187" t="s">
-        <v>55</v>
-      </c>
       <c r="C187" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4530,13 +4530,13 @@
     </row>
     <row r="188" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>53</v>
+      </c>
+      <c r="B188" t="s">
         <v>54</v>
       </c>
-      <c r="B188" t="s">
-        <v>55</v>
-      </c>
       <c r="C188" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -4544,13 +4544,13 @@
     </row>
     <row r="189" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>53</v>
+      </c>
+      <c r="B189" t="s">
         <v>54</v>
       </c>
-      <c r="B189" t="s">
-        <v>55</v>
-      </c>
       <c r="C189" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -4558,13 +4558,13 @@
     </row>
     <row r="190" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>53</v>
+      </c>
+      <c r="B190" t="s">
         <v>54</v>
       </c>
-      <c r="B190" t="s">
-        <v>55</v>
-      </c>
       <c r="C190" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -4572,13 +4572,13 @@
     </row>
     <row r="191" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>53</v>
+      </c>
+      <c r="B191" t="s">
         <v>54</v>
       </c>
-      <c r="B191" t="s">
-        <v>55</v>
-      </c>
       <c r="C191" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -4586,13 +4586,13 @@
     </row>
     <row r="192" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>53</v>
+      </c>
+      <c r="B192" t="s">
         <v>54</v>
       </c>
-      <c r="B192" t="s">
-        <v>55</v>
-      </c>
       <c r="C192" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -4600,13 +4600,13 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -4614,13 +4614,13 @@
     </row>
     <row r="194" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B194" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4628,13 +4628,13 @@
     </row>
     <row r="195" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -4642,13 +4642,13 @@
     </row>
     <row r="196" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -4656,13 +4656,13 @@
     </row>
     <row r="197" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B197" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -4670,13 +4670,13 @@
     </row>
     <row r="198" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -4684,13 +4684,13 @@
     </row>
     <row r="199" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B199" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="200" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B200" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -4712,13 +4712,13 @@
     </row>
     <row r="201" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B201" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -4726,13 +4726,13 @@
     </row>
     <row r="202" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B202" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -4740,13 +4740,13 @@
     </row>
     <row r="203" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -4754,13 +4754,13 @@
     </row>
     <row r="204" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -4768,13 +4768,13 @@
     </row>
     <row r="205" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B205" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -4782,13 +4782,13 @@
     </row>
     <row r="206" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -4796,13 +4796,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B207" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C207" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -4810,13 +4810,13 @@
     </row>
     <row r="208" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -4824,13 +4824,13 @@
     </row>
     <row r="209" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -4838,13 +4838,13 @@
     </row>
     <row r="210" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="211" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B211" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -4866,13 +4866,13 @@
     </row>
     <row r="212" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -4880,13 +4880,13 @@
     </row>
     <row r="213" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B213" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -4894,13 +4894,13 @@
     </row>
     <row r="214" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>227</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B214" t="s">
-        <v>12</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -4908,13 +4908,13 @@
     </row>
     <row r="215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B215" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -4922,13 +4922,13 @@
     </row>
     <row r="216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B216" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -4936,13 +4936,13 @@
     </row>
     <row r="217" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="218" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B218" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -4964,13 +4964,13 @@
     </row>
     <row r="219" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -4978,13 +4978,13 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B220" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C220" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -4992,13 +4992,13 @@
     </row>
     <row r="221" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B221" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5006,13 +5006,13 @@
     </row>
     <row r="222" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D222">
         <v>1</v>
@@ -5020,13 +5020,13 @@
     </row>
     <row r="223" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B223" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -5034,13 +5034,13 @@
     </row>
     <row r="224" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -5048,13 +5048,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B225" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -5062,13 +5062,13 @@
     </row>
     <row r="226" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B226" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5076,13 +5076,13 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C227" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -5090,13 +5090,13 @@
     </row>
     <row r="228" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -5104,13 +5104,13 @@
     </row>
     <row r="229" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -5118,13 +5118,13 @@
     </row>
     <row r="230" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B230" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -5132,13 +5132,13 @@
     </row>
     <row r="231" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
+        <v>245</v>
+      </c>
+      <c r="B231" t="s">
+        <v>27</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B231" t="s">
-        <v>28</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -5146,13 +5146,13 @@
     </row>
     <row r="232" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B232" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5160,13 +5160,13 @@
     </row>
     <row r="233" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B233" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -5174,13 +5174,13 @@
     </row>
     <row r="234" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B234" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -5188,13 +5188,13 @@
     </row>
     <row r="235" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -5202,13 +5202,13 @@
     </row>
     <row r="236" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B236" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -5216,13 +5216,13 @@
     </row>
     <row r="237" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B237" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -5230,13 +5230,13 @@
     </row>
     <row r="238" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -5244,13 +5244,13 @@
     </row>
     <row r="239" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -5258,13 +5258,13 @@
     </row>
     <row r="240" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -5272,13 +5272,13 @@
     </row>
     <row r="241" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B241" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -5286,13 +5286,13 @@
     </row>
     <row r="242" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -5300,13 +5300,13 @@
     </row>
     <row r="243" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -5314,13 +5314,13 @@
     </row>
     <row r="244" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -5328,13 +5328,13 @@
     </row>
     <row r="245" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -5342,13 +5342,13 @@
     </row>
     <row r="246" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B246" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -5356,13 +5356,13 @@
     </row>
     <row r="247" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -5370,13 +5370,13 @@
     </row>
     <row r="248" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B248" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -5384,13 +5384,13 @@
     </row>
     <row r="249" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B249" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D249">
         <v>1</v>
@@ -5398,13 +5398,13 @@
     </row>
     <row r="250" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B250" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -5412,13 +5412,13 @@
     </row>
     <row r="251" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B251" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -5426,13 +5426,13 @@
     </row>
     <row r="252" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B252" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -5440,13 +5440,13 @@
     </row>
     <row r="253" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B253" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -5454,13 +5454,13 @@
     </row>
     <row r="254" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B254" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -5468,13 +5468,13 @@
     </row>
     <row r="255" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B255" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -5482,13 +5482,13 @@
     </row>
     <row r="256" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B256" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D256">
         <v>1</v>
@@ -5496,13 +5496,13 @@
     </row>
     <row r="257" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B257" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -5510,13 +5510,13 @@
     </row>
     <row r="258" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B258" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -5524,13 +5524,13 @@
     </row>
     <row r="259" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B259" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -5538,13 +5538,13 @@
     </row>
     <row r="260" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B260" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D260">
         <v>1</v>
@@ -5552,13 +5552,13 @@
     </row>
     <row r="261" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B261" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -5566,13 +5566,13 @@
     </row>
     <row r="262" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B262" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -5580,13 +5580,13 @@
     </row>
     <row r="263" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B263" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -5594,13 +5594,13 @@
     </row>
     <row r="264" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -5608,13 +5608,13 @@
     </row>
     <row r="265" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -5622,13 +5622,13 @@
     </row>
     <row r="266" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -5636,13 +5636,13 @@
     </row>
     <row r="267" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -5650,13 +5650,13 @@
     </row>
     <row r="268" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D268">
         <v>0</v>
@@ -5664,13 +5664,13 @@
     </row>
     <row r="269" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -5678,13 +5678,13 @@
     </row>
     <row r="270" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B270" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -5692,13 +5692,13 @@
     </row>
     <row r="271" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -5706,13 +5706,13 @@
     </row>
     <row r="272" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B272" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -5720,13 +5720,13 @@
     </row>
     <row r="273" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B273" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -5734,13 +5734,13 @@
     </row>
     <row r="274" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B274" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D274">
         <v>0</v>
@@ -5748,13 +5748,13 @@
     </row>
     <row r="275" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B275" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -5762,13 +5762,13 @@
     </row>
     <row r="276" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B276" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="277" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B277" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -5790,13 +5790,13 @@
     </row>
     <row r="278" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B278" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -5804,13 +5804,13 @@
     </row>
     <row r="279" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B279" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -5818,13 +5818,13 @@
     </row>
     <row r="280" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B280" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -5832,13 +5832,13 @@
     </row>
     <row r="281" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B281" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -5846,13 +5846,13 @@
     </row>
     <row r="282" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B282" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -5860,13 +5860,13 @@
     </row>
     <row r="283" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B283" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -5874,13 +5874,13 @@
     </row>
     <row r="284" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B284" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -5888,13 +5888,13 @@
     </row>
     <row r="285" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B285" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -5902,13 +5902,13 @@
     </row>
     <row r="286" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B286" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -5916,13 +5916,13 @@
     </row>
     <row r="287" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B287" t="s">
+        <v>303</v>
+      </c>
+      <c r="C287" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C287" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="D287">
         <v>1</v>
@@ -5930,13 +5930,13 @@
     </row>
     <row r="288" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B288" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -5944,13 +5944,13 @@
     </row>
     <row r="289" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B289" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -5958,13 +5958,13 @@
     </row>
     <row r="290" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B290" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D290">
         <v>1</v>
@@ -5972,13 +5972,13 @@
     </row>
     <row r="291" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B291" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -5986,13 +5986,13 @@
     </row>
     <row r="292" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B292" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -6000,13 +6000,13 @@
     </row>
     <row r="293" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B293" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -6014,13 +6014,13 @@
     </row>
     <row r="294" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B294" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D294">
         <v>1</v>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="295" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B295" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D295">
         <v>1</v>
@@ -6042,13 +6042,13 @@
     </row>
     <row r="296" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B296" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D296">
         <v>1</v>
@@ -6056,13 +6056,13 @@
     </row>
     <row r="297" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B297" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -6070,13 +6070,13 @@
     </row>
     <row r="298" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>315</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B298" t="s">
-        <v>5</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="D298">
         <v>1</v>
@@ -6084,13 +6084,13 @@
     </row>
     <row r="299" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B299" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -6098,13 +6098,13 @@
     </row>
     <row r="300" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B300" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -6112,13 +6112,13 @@
     </row>
     <row r="301" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B301" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D301">
         <v>1</v>
@@ -6126,13 +6126,13 @@
     </row>
     <row r="302" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B302" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -6140,13 +6140,13 @@
     </row>
     <row r="303" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B303" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D303">
         <v>1</v>
@@ -6154,13 +6154,13 @@
     </row>
     <row r="304" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B304" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D304">
         <v>1</v>
@@ -6168,13 +6168,13 @@
     </row>
     <row r="305" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B305" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -6182,13 +6182,13 @@
     </row>
     <row r="306" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B306" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D306">
         <v>1</v>
@@ -6196,13 +6196,13 @@
     </row>
     <row r="307" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B307" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D307">
         <v>1</v>
@@ -6210,13 +6210,13 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B308" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C308" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -6224,13 +6224,13 @@
     </row>
     <row r="309" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B309" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D309">
         <v>1</v>
@@ -6238,13 +6238,13 @@
     </row>
     <row r="310" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B310" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D310">
         <v>1</v>
@@ -6252,13 +6252,13 @@
     </row>
     <row r="311" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B311" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -6266,13 +6266,13 @@
     </row>
     <row r="312" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B312" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -6280,13 +6280,13 @@
     </row>
     <row r="313" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
+        <v>332</v>
+      </c>
+      <c r="B313" t="s">
+        <v>333</v>
+      </c>
+      <c r="C313" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B313" t="s">
-        <v>335</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -6294,13 +6294,13 @@
     </row>
     <row r="314" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B314" t="s">
+        <v>333</v>
+      </c>
+      <c r="C314" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="D314">
         <v>1</v>
@@ -6308,13 +6308,13 @@
     </row>
     <row r="315" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D315">
         <v>1</v>
@@ -6322,13 +6322,13 @@
     </row>
     <row r="316" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B316" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D316">
         <v>1</v>
@@ -6336,13 +6336,13 @@
     </row>
     <row r="317" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B317" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D317">
         <v>1</v>
@@ -6350,13 +6350,13 @@
     </row>
     <row r="318" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B318" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -6364,13 +6364,13 @@
     </row>
     <row r="319" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B319" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -6378,13 +6378,13 @@
     </row>
     <row r="320" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B320" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -6392,13 +6392,13 @@
     </row>
     <row r="321" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B321" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -6406,13 +6406,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B322" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D322">
         <v>0</v>
@@ -6420,13 +6420,13 @@
     </row>
     <row r="323" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B323" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -6434,13 +6434,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B324" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -6448,13 +6448,13 @@
     </row>
     <row r="325" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B325" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -6462,13 +6462,13 @@
     </row>
     <row r="326" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B326" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D326">
         <v>1</v>
@@ -6476,13 +6476,13 @@
     </row>
     <row r="327" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B327" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D327">
         <v>1</v>
@@ -6490,13 +6490,13 @@
     </row>
     <row r="328" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B328" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D328">
         <v>0</v>
@@ -6504,13 +6504,13 @@
     </row>
     <row r="329" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B329" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D329">
         <v>0</v>
@@ -6518,13 +6518,13 @@
     </row>
     <row r="330" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B330" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -6532,13 +6532,13 @@
     </row>
     <row r="331" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B331" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -6546,13 +6546,13 @@
     </row>
     <row r="332" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B332" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D332">
         <v>0</v>
@@ -6560,13 +6560,13 @@
     </row>
     <row r="333" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D333">
         <v>1</v>
@@ -6574,13 +6574,13 @@
     </row>
     <row r="334" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D334">
         <v>1</v>
@@ -6588,13 +6588,13 @@
     </row>
     <row r="335" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D335">
         <v>1</v>

--- a/annotations JL.xlsx
+++ b/annotations JL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jean-\Desktop\Cours ENSAE\3A ENSAE\NLP\Projet final\NLP_ENSAE_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1807FCE5-3E91-42D3-AEE5-C58A23E32E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B428A186-10A4-47C5-B821-549B819C08F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{89D58ADA-68C1-4510-AD5E-1C4D340B6593}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{89D58ADA-68C1-4510-AD5E-1C4D340B6593}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="358">
   <si>
     <t>Parti</t>
   </si>
@@ -776,10 +776,6 @@
 · Pour en finir avec l'amalgame "lutte contre l'alcoolisme = lutte contre le vin", nous prendrons appui sur cette loi et ferons parrainer nos crus avec talent.</t>
   </si>
   <si>
-    <t>· Pour étendre la réputation de nos vins jusque dans le grand public et parce que les modes de consommation ne sont pas une fatalité, frappons un grand coup avec la TGD, la "Très Grande Dégustation".
-· Pour aider les jeunes viticulteurs à s'installer, créons des Sociétés de Financement de la Vigne et de ses Equipements, sur le modèle astucieux de ce qui a été fait dans l'hôtellerie, la distribution et l'immobilier commercial.</t>
-  </si>
-  <si>
     <t>· Pour tous et parce que les viticulteurs ont joué le jeu de la qualité et de l'auto- discipline, exigeons le contrôle le plus strict des vins d'importation, afin de garantir nos revenus et préparer l'avenir.</t>
   </si>
   <si>
@@ -1325,9 +1321,6 @@
 Avec Robert CELAIRE</t>
   </si>
   <si>
-    <t>GD</t>
-  </si>
-  <si>
     <t>Madame, Mademoiselle, Monsieur,
 Nous sommes des millions d'hommes et de femmes à rejeter la politique actuelle qui nous fait si mal, à refuser la droite qui ferait pire, à chercher un autre chemin qui ne conduise pas demain à de nouvelles déceptions.</t>
   </si>
@@ -1522,6 +1515,10 @@
   </si>
   <si>
     <t>Courant Politique</t>
+  </si>
+  <si>
+    <t>· Pour étendre la réputation de nos vins jusque dans le grand public et parce que les modes de consommation ne sont pas une fatalité, frappons un grand coup avec la TGR, la "Très Grande Dégustation".
+· Pour aider les jeunes viticulteurs à s'installer, créons des Sociétés de Financement de la Vigne et de ses Equipements, sur le modèle astucieux de ce qui a été fait dans l'hôtellerie, la distribution et l'immobilier commercial.</t>
   </si>
 </sst>
 </file>
@@ -1915,13 +1912,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -3942,7 +3939,7 @@
     </row>
     <row r="146" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B146" t="s">
         <v>11</v>
@@ -3956,7 +3953,7 @@
     </row>
     <row r="147" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B147" t="s">
         <v>11</v>
@@ -3970,13 +3967,13 @@
     </row>
     <row r="148" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B148" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>160</v>
+        <v>357</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -3984,13 +3981,13 @@
     </row>
     <row r="149" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B149" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -3998,13 +3995,13 @@
     </row>
     <row r="150" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B150" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4012,13 +4009,13 @@
     </row>
     <row r="151" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
         <v>11</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4026,13 +4023,13 @@
     </row>
     <row r="152" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B152" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4040,13 +4037,13 @@
     </row>
     <row r="153" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B153" t="s">
         <v>11</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -4054,13 +4051,13 @@
     </row>
     <row r="154" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B154" t="s">
         <v>11</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4068,13 +4065,13 @@
     </row>
     <row r="155" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B155" t="s">
         <v>11</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4082,13 +4079,13 @@
     </row>
     <row r="156" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B156" t="s">
         <v>11</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4096,13 +4093,13 @@
     </row>
     <row r="157" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>169</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B157" t="s">
-        <v>11</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -4110,13 +4107,13 @@
     </row>
     <row r="158" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B158" t="s">
         <v>11</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -4124,13 +4121,13 @@
     </row>
     <row r="159" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B159" t="s">
         <v>11</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -4138,13 +4135,13 @@
     </row>
     <row r="160" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B160" t="s">
         <v>11</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -4158,7 +4155,7 @@
         <v>4</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -4172,7 +4169,7 @@
         <v>4</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -4186,7 +4183,7 @@
         <v>4</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -4200,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -4214,7 +4211,7 @@
         <v>4</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -4228,7 +4225,7 @@
         <v>4</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -4242,7 +4239,7 @@
         <v>4</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -4256,7 +4253,7 @@
         <v>4</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -4270,7 +4267,7 @@
         <v>4</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -4284,7 +4281,7 @@
         <v>4</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -4298,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4312,7 +4309,7 @@
         <v>4</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -4326,7 +4323,7 @@
         <v>4</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -4340,7 +4337,7 @@
         <v>4</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4354,7 +4351,7 @@
         <v>4</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -4368,7 +4365,7 @@
         <v>4</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -4382,7 +4379,7 @@
         <v>4</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -4396,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -4410,7 +4407,7 @@
         <v>4</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -4424,7 +4421,7 @@
         <v>27</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -4438,7 +4435,7 @@
         <v>27</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -4452,7 +4449,7 @@
         <v>27</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -4466,7 +4463,7 @@
         <v>27</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -4480,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -4494,7 +4491,7 @@
         <v>27</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4508,7 +4505,7 @@
         <v>54</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -4522,7 +4519,7 @@
         <v>54</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4536,7 +4533,7 @@
         <v>54</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -4550,7 +4547,7 @@
         <v>54</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -4564,7 +4561,7 @@
         <v>54</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -4578,7 +4575,7 @@
         <v>54</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -4592,7 +4589,7 @@
         <v>54</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -4606,7 +4603,7 @@
         <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -4620,7 +4617,7 @@
         <v>11</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4634,7 +4631,7 @@
         <v>11</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -4648,7 +4645,7 @@
         <v>11</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -4662,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -4676,7 +4673,7 @@
         <v>11</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -4690,7 +4687,7 @@
         <v>11</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -4704,7 +4701,7 @@
         <v>11</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -4718,7 +4715,7 @@
         <v>11</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -4732,7 +4729,7 @@
         <v>11</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -4746,7 +4743,7 @@
         <v>11</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -4760,7 +4757,7 @@
         <v>11</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -4774,7 +4771,7 @@
         <v>11</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -4788,7 +4785,7 @@
         <v>11</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -4802,7 +4799,7 @@
         <v>11</v>
       </c>
       <c r="C207" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -4816,7 +4813,7 @@
         <v>11</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -4830,7 +4827,7 @@
         <v>11</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -4844,7 +4841,7 @@
         <v>11</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -4858,7 +4855,7 @@
         <v>11</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -4872,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -4880,13 +4877,13 @@
     </row>
     <row r="213" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>226</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B213" t="s">
-        <v>11</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -4894,13 +4891,13 @@
     </row>
     <row r="214" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B214" t="s">
         <v>11</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -4908,13 +4905,13 @@
     </row>
     <row r="215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B215" t="s">
         <v>11</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -4922,13 +4919,13 @@
     </row>
     <row r="216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B216" t="s">
         <v>11</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -4936,13 +4933,13 @@
     </row>
     <row r="217" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B217" t="s">
         <v>11</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -4950,13 +4947,13 @@
     </row>
     <row r="218" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B218" t="s">
         <v>11</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -4964,13 +4961,13 @@
     </row>
     <row r="219" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B219" t="s">
         <v>11</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -4978,13 +4975,13 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B220" t="s">
         <v>11</v>
       </c>
       <c r="C220" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -4992,13 +4989,13 @@
     </row>
     <row r="221" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B221" t="s">
         <v>11</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5006,13 +5003,13 @@
     </row>
     <row r="222" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B222" t="s">
         <v>11</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D222">
         <v>1</v>
@@ -5020,13 +5017,13 @@
     </row>
     <row r="223" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B223" t="s">
         <v>11</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -5034,13 +5031,13 @@
     </row>
     <row r="224" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B224" t="s">
         <v>11</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -5048,13 +5045,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B225" t="s">
         <v>11</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -5062,13 +5059,13 @@
     </row>
     <row r="226" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B226" t="s">
         <v>11</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5076,13 +5073,13 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B227" t="s">
         <v>11</v>
       </c>
       <c r="C227" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -5090,13 +5087,13 @@
     </row>
     <row r="228" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B228" t="s">
         <v>11</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -5104,13 +5101,13 @@
     </row>
     <row r="229" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B229" t="s">
         <v>11</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -5118,13 +5115,13 @@
     </row>
     <row r="230" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B230" t="s">
         <v>27</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -5132,13 +5129,13 @@
     </row>
     <row r="231" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B231" t="s">
         <v>27</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -5146,13 +5143,13 @@
     </row>
     <row r="232" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B232" t="s">
         <v>27</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5160,13 +5157,13 @@
     </row>
     <row r="233" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B233" t="s">
         <v>27</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -5174,13 +5171,13 @@
     </row>
     <row r="234" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B234" t="s">
         <v>27</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -5188,13 +5185,13 @@
     </row>
     <row r="235" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B235" t="s">
         <v>27</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -5208,7 +5205,7 @@
         <v>4</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -5222,7 +5219,7 @@
         <v>4</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -5236,7 +5233,7 @@
         <v>4</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -5250,7 +5247,7 @@
         <v>4</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -5264,7 +5261,7 @@
         <v>4</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -5278,7 +5275,7 @@
         <v>4</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -5292,7 +5289,7 @@
         <v>4</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -5306,7 +5303,7 @@
         <v>4</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -5320,7 +5317,7 @@
         <v>4</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -5334,7 +5331,7 @@
         <v>4</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -5348,7 +5345,7 @@
         <v>4</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -5356,13 +5353,13 @@
     </row>
     <row r="247" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B247" t="s">
         <v>4</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -5370,13 +5367,13 @@
     </row>
     <row r="248" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B248" t="s">
         <v>4</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -5384,13 +5381,13 @@
     </row>
     <row r="249" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B249" t="s">
         <v>4</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D249">
         <v>1</v>
@@ -5398,13 +5395,13 @@
     </row>
     <row r="250" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B250" t="s">
         <v>4</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -5412,13 +5409,13 @@
     </row>
     <row r="251" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B251" t="s">
         <v>4</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -5426,13 +5423,13 @@
     </row>
     <row r="252" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B252" t="s">
         <v>4</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -5440,13 +5437,13 @@
     </row>
     <row r="253" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B253" t="s">
         <v>4</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -5460,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -5474,7 +5471,7 @@
         <v>4</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -5488,7 +5485,7 @@
         <v>4</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D256">
         <v>1</v>
@@ -5502,7 +5499,7 @@
         <v>4</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -5516,7 +5513,7 @@
         <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -5530,7 +5527,7 @@
         <v>4</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -5544,7 +5541,7 @@
         <v>4</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D260">
         <v>1</v>
@@ -5558,7 +5555,7 @@
         <v>4</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -5572,7 +5569,7 @@
         <v>4</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -5586,7 +5583,7 @@
         <v>4</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -5600,7 +5597,7 @@
         <v>4</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -5614,7 +5611,7 @@
         <v>4</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -5628,7 +5625,7 @@
         <v>4</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -5642,7 +5639,7 @@
         <v>4</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -5656,7 +5653,7 @@
         <v>4</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D268">
         <v>0</v>
@@ -5670,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -5684,7 +5681,7 @@
         <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -5698,7 +5695,7 @@
         <v>4</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -5712,7 +5709,7 @@
         <v>4</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -5726,7 +5723,7 @@
         <v>4</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -5740,7 +5737,7 @@
         <v>4</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D274">
         <v>0</v>
@@ -5754,7 +5751,7 @@
         <v>4</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -5768,7 +5765,7 @@
         <v>4</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -5782,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -5796,7 +5793,7 @@
         <v>4</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -5810,7 +5807,7 @@
         <v>4</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -5824,7 +5821,7 @@
         <v>4</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -5838,7 +5835,7 @@
         <v>4</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -5852,7 +5849,7 @@
         <v>4</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -5866,7 +5863,7 @@
         <v>4</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -5880,7 +5877,7 @@
         <v>4</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -5894,7 +5891,7 @@
         <v>4</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -5905,10 +5902,10 @@
         <v>53</v>
       </c>
       <c r="B286" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -5919,10 +5916,10 @@
         <v>53</v>
       </c>
       <c r="B287" t="s">
+        <v>54</v>
+      </c>
+      <c r="C287" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="C287" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="D287">
         <v>1</v>
@@ -5933,10 +5930,10 @@
         <v>53</v>
       </c>
       <c r="B288" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -5947,10 +5944,10 @@
         <v>53</v>
       </c>
       <c r="B289" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -5961,10 +5958,10 @@
         <v>53</v>
       </c>
       <c r="B290" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D290">
         <v>1</v>
@@ -5975,10 +5972,10 @@
         <v>53</v>
       </c>
       <c r="B291" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -5989,10 +5986,10 @@
         <v>53</v>
       </c>
       <c r="B292" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -6003,10 +6000,10 @@
         <v>53</v>
       </c>
       <c r="B293" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -6017,10 +6014,10 @@
         <v>53</v>
       </c>
       <c r="B294" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D294">
         <v>1</v>
@@ -6031,10 +6028,10 @@
         <v>53</v>
       </c>
       <c r="B295" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D295">
         <v>1</v>
@@ -6042,13 +6039,13 @@
     </row>
     <row r="296" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B296" t="s">
         <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D296">
         <v>1</v>
@@ -6056,13 +6053,13 @@
     </row>
     <row r="297" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B297" t="s">
         <v>4</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -6070,13 +6067,13 @@
     </row>
     <row r="298" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>313</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B298" t="s">
-        <v>4</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="D298">
         <v>1</v>
@@ -6084,13 +6081,13 @@
     </row>
     <row r="299" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B299" t="s">
         <v>4</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -6098,13 +6095,13 @@
     </row>
     <row r="300" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B300" t="s">
         <v>4</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -6112,13 +6109,13 @@
     </row>
     <row r="301" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B301" t="s">
         <v>4</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D301">
         <v>1</v>
@@ -6132,7 +6129,7 @@
         <v>11</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -6146,7 +6143,7 @@
         <v>11</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D303">
         <v>1</v>
@@ -6160,7 +6157,7 @@
         <v>11</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D304">
         <v>1</v>
@@ -6174,7 +6171,7 @@
         <v>11</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -6188,7 +6185,7 @@
         <v>11</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D306">
         <v>1</v>
@@ -6202,7 +6199,7 @@
         <v>11</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D307">
         <v>1</v>
@@ -6216,7 +6213,7 @@
         <v>4</v>
       </c>
       <c r="C308" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -6230,7 +6227,7 @@
         <v>4</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D309">
         <v>1</v>
@@ -6244,7 +6241,7 @@
         <v>4</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D310">
         <v>1</v>
@@ -6258,7 +6255,7 @@
         <v>4</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -6272,7 +6269,7 @@
         <v>4</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -6280,13 +6277,13 @@
     </row>
     <row r="313" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
+        <v>330</v>
+      </c>
+      <c r="B313" t="s">
+        <v>331</v>
+      </c>
+      <c r="C313" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B313" t="s">
-        <v>333</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -6294,13 +6291,13 @@
     </row>
     <row r="314" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B314" t="s">
+        <v>331</v>
+      </c>
+      <c r="C314" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="D314">
         <v>1</v>
@@ -6308,13 +6305,13 @@
     </row>
     <row r="315" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B315" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D315">
         <v>1</v>
@@ -6322,13 +6319,13 @@
     </row>
     <row r="316" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B316" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D316">
         <v>1</v>
@@ -6336,13 +6333,13 @@
     </row>
     <row r="317" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B317" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D317">
         <v>1</v>
@@ -6350,13 +6347,13 @@
     </row>
     <row r="318" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B318" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -6364,13 +6361,13 @@
     </row>
     <row r="319" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B319" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -6378,13 +6375,13 @@
     </row>
     <row r="320" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B320" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -6392,13 +6389,13 @@
     </row>
     <row r="321" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B321" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -6406,13 +6403,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B322" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D322">
         <v>0</v>
@@ -6420,13 +6417,13 @@
     </row>
     <row r="323" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B323" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -6434,13 +6431,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B324" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -6448,13 +6445,13 @@
     </row>
     <row r="325" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B325" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -6462,13 +6459,13 @@
     </row>
     <row r="326" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B326" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D326">
         <v>1</v>
@@ -6476,13 +6473,13 @@
     </row>
     <row r="327" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B327" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D327">
         <v>1</v>
@@ -6490,13 +6487,13 @@
     </row>
     <row r="328" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B328" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D328">
         <v>0</v>
@@ -6504,13 +6501,13 @@
     </row>
     <row r="329" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B329" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D329">
         <v>0</v>
@@ -6518,13 +6515,13 @@
     </row>
     <row r="330" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B330" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -6532,13 +6529,13 @@
     </row>
     <row r="331" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -6546,13 +6543,13 @@
     </row>
     <row r="332" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D332">
         <v>0</v>
@@ -6560,13 +6557,13 @@
     </row>
     <row r="333" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D333">
         <v>1</v>
@@ -6574,13 +6571,13 @@
     </row>
     <row r="334" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D334">
         <v>1</v>
@@ -6588,13 +6585,13 @@
     </row>
     <row r="335" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D335">
         <v>1</v>
